--- a/docs/Diccionario_de_datos_TallerDatos_entrega2.xlsx
+++ b/docs/Diccionario_de_datos_TallerDatos_entrega2.xlsx
@@ -624,7 +624,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Actualizado el 2026-10-25 por ingesta/diccionario.py desde el lago. La hoja «Cambios entrega 2» lista cada cambio frente a la entrega 1, y la hoja «Protección» qué trae cada fuente sobre personas y qué llega al lago.</t>
+          <t>Actualizado el 2026-10-26 por ingesta/diccionario.py desde el lago. La hoja «Cambios entrega 2» lista cada cambio frente a la entrega 1, y la hoja «Protección» qué trae cada fuente sobre personas y qué llega al lago.</t>
         </is>
       </c>
     </row>
@@ -18004,17 +18004,17 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Abrió la demo y subió el GeoJSON, pero el clic en «Add Data» no se completó en un Chrome sin ventana</t>
+          <t>Abrió la demo y subió el GeoJSON, pero el clic en «Add Data» no se completó en un Chrome sin ventana; el grupo lo terminó a mano</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Capturas de cada paso (exploracion/kepler)</t>
+          <t>Capturas de cada paso (exploracion/kepler) y la prueba a mano de Juan Jose</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>Queda pendiente terminar la prueba a mano en un navegador normal.</t>
+          <t>La IA no logró automatizar el último paso. Ya en el navegador, kepler eligió una escala por cuantiles que no muestra magnitudes y no lleva el ID de la fuente.</t>
         </is>
       </c>
     </row>

--- a/docs/Diccionario_de_datos_TallerDatos_entrega2.xlsx
+++ b/docs/Diccionario_de_datos_TallerDatos_entrega2.xlsx
@@ -18004,12 +18004,12 @@
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Abrió la demo y subió el GeoJSON, pero el clic en «Add Data» no se completó en un Chrome sin ventana; el grupo lo terminó a mano</t>
+          <t>Abrió la demo y subió el GeoJSON, pero el clic en «Add Data» no se completó en un Chrome sin ventana; Samuel lo terminó a mano</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>Capturas de cada paso (exploracion/kepler) y la prueba a mano de Juan Jose</t>
+          <t>Capturas de cada paso (exploracion/kepler) y la prueba a mano de Samuel</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
